--- a/output/北塩原村_現行計画評価.xlsx
+++ b/output/北塩原村_現行計画評価.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_見込量と実績の突合'!$A$5:$L$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_地域生活支援事業'!$A$5:$K$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_地域生活支援事業'!$A$5:$K$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -778,7 +778,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>令和3〜5年度の実績と見込量の対比（13事業）</t>
+          <t>令和3〜5年度の実績と見込量の対比（16事業）</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3826,8 +3826,143 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>訪問入浴サービス事業（任意）</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>実績・見込とも0</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>任意事業。重度化・高齢化が進む中でニーズの有無を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>日中一時支援事業（任意）</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>見込を上回る</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>任意事業。前計画は3年間とも見込0だが実績は1〜2人。令和6年度以降は2人へ是正済み。現行計画本文も「増加傾向」と記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>福祉ホーム事業（任意）</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>見込を上回る</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>任意事業。前計画は見込0だが実績は1〜2人で推移。それにもかかわらず令和6〜8年度の見込量も0人としており、実績があるのに見込を置いていない状態。次期計画で是正が必要</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:K18"/>
+  <autoFilter ref="A5:K21"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>

--- a/output/北塩原村_現行計画評価.xlsx
+++ b/output/北塩原村_現行計画評価.xlsx
@@ -2674,7 +2674,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>協議の場・コーディネーターの設置状況は村資料待ち</t>
+          <t>医療的ケア児1人は令和8年8月の村の朱書きで再確認（経管栄養が毎日必要）。障がい児入所施設・児童福祉施設の利用児0件、障害児通所支援の申請中0件も確認。協議の場・コーディネーターの設置状況は村資料待ち</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>設置状況は村資料待ち。計画相談支援の実績は見込どおりで推移</t>
+          <t>基幹相談支援センターは令和8年8月時点で未設置。目標1か所は未達。計画相談支援の実績は見込どおりで推移</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>第8期は「のぞまないセルフプラン」の件数を令和11年度末までに0とすることが新規。村内にセルフプラン利用者がいないことを7月7日打合せで確認済み</t>
+          <t>第8期は「のぞまないセルフプラン」の件数を令和11年度末までに0とすることが新規。セルフプラン率0％を令和8年8月の村の朱書きで再確認したため、目標は「0を維持」となる。基幹相談支援センターは4町村での広域設置の検討状況を踏まえ目標年次を再設定する</t>
         </is>
       </c>
     </row>
@@ -3084,12 +3084,12 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>―（防災部局の作成状況）</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>測定可能</t>
+          <t>―（防災部局の作成状況）※令和8年8月の村の朱書きでは「作成者なし（0件）」。策定時の1件が失効したのか集計方法が異なるのかを要確認（進捗管理 R-18）</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
     </row>
